--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\microsoft-bot-account\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60D9F07-C96D-4AB2-94CE-2383F1F21014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC383FB-8AEC-4FB5-9CD3-116D65194E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,7 +187,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -221,9 +221,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -564,7 +564,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.796875" customWidth="1"/>
     <col min="2" max="2" width="35.796875" customWidth="1"/>
@@ -582,162 +582,162 @@
     <col min="16" max="17" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\microsoft-bot-account\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC383FB-8AEC-4FB5-9CD3-116D65194E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141ACF1B-00CA-4030-B7D4-A077AAE7203B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>Email</t>
   </si>
@@ -155,13 +155,31 @@
   </si>
   <si>
     <t>55455</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Domain Email</t>
+  </si>
+  <si>
+    <t>SUCCESS</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>orion@detroitauto.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>peregrine.quinn@minneapolismedical.onmicrosoft.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -173,6 +191,14 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -192,7 +218,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -200,32 +226,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -563,187 +581,212 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.796875" customWidth="1"/>
-    <col min="2" max="2" width="35.796875" customWidth="1"/>
-    <col min="3" max="4" width="15.796875" customWidth="1"/>
-    <col min="5" max="5" width="30.796875" customWidth="1"/>
-    <col min="6" max="6" width="12.796875" customWidth="1"/>
-    <col min="7" max="7" width="16.796875" customWidth="1"/>
-    <col min="8" max="8" width="22.796875" customWidth="1"/>
-    <col min="9" max="9" width="25.796875" customWidth="1"/>
-    <col min="10" max="11" width="15.796875" customWidth="1"/>
-    <col min="12" max="12" width="12.796875" customWidth="1"/>
-    <col min="13" max="13" width="15.796875" customWidth="1"/>
-    <col min="14" max="14" width="20.796875" customWidth="1"/>
-    <col min="15" max="15" width="6.796875" customWidth="1"/>
-    <col min="16" max="17" width="10.796875" customWidth="1"/>
+    <col min="1" max="1" width="40.796875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="35.796875" style="3" customWidth="1"/>
+    <col min="3" max="4" width="15.796875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.796875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.796875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.796875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="22.796875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="25.796875" style="3" customWidth="1"/>
+    <col min="10" max="11" width="15.796875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="12.796875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.796875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.796875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="6.796875" style="3" customWidth="1"/>
+    <col min="16" max="17" width="10.796875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="8.796875" style="3"/>
+    <col min="19" max="19" width="41.69921875" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="8.796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="R2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" s="3" t="s">
         <v>33</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="S2" r:id="rId1" xr:uid="{C8446FB8-1840-4888-8988-27E43A0D4858}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{AB3EEAB8-1F91-412B-AB06-914CAC2A7890}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:Q3" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:T5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,43 +457,46 @@
       <c r="S1" t="str">
         <v>Domain Email</v>
       </c>
+      <c r="T1" t="str">
+        <v>Log</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>orion.wren@detroitautomotive.us</v>
+        <v>ursula.vance@neworleansresearch.us</v>
       </c>
       <c r="B2" t="str">
-        <v>AutoOrion6789@Detroit</v>
+        <v>ResearchUrsula6789@NewOrleans</v>
       </c>
       <c r="C2" t="str">
-        <v>Orion</v>
+        <v>Ursula</v>
       </c>
       <c r="D2" t="str">
-        <v>Wren</v>
+        <v>Vance</v>
       </c>
       <c r="E2" t="str">
-        <v>Detroit Automotive Design</v>
+        <v>New Orleans Research Center</v>
       </c>
       <c r="F2" t="str">
         <v>1 person</v>
       </c>
       <c r="G2" t="str">
-        <v>+13135556789</v>
+        <v>+15045556789</v>
       </c>
       <c r="H2" t="str">
-        <v>Automotive Engineer</v>
+        <v>Clinical Researcher</v>
       </c>
       <c r="I2" t="str">
-        <v>1500 Woodward Avenue</v>
+        <v>1440 Canal Street</v>
       </c>
       <c r="J2" t="str">
-        <v>Detroit</v>
+        <v>New Orleans</v>
       </c>
       <c r="K2" t="str">
-        <v>Michigan</v>
+        <v>Louisiana</v>
       </c>
       <c r="L2" t="str">
-        <v>48226</v>
+        <v>70112</v>
       </c>
       <c r="M2" t="str">
         <v>United States</v>
@@ -515,44 +518,47 @@
       </c>
       <c r="S2" t="str">
         <v/>
+      </c>
+      <c r="T2" t="str">
+        <v>Step: Saving payment - Error: PAYMENT_DECLINED: Check that the details in all fields are correct or try a different card.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>peregrine.quinn@minneapolismedical.us</v>
+        <v>vesper.grey@tampaport.us</v>
       </c>
       <c r="B3" t="str">
-        <v>MedicalPeregrine1234@Minneapolis</v>
+        <v>PortVesper1234@Tampa</v>
       </c>
       <c r="C3" t="str">
-        <v>Peregrine</v>
+        <v>Vesper</v>
       </c>
       <c r="D3" t="str">
-        <v>Quinn</v>
+        <v>Grey</v>
       </c>
       <c r="E3" t="str">
-        <v>Minneapolis Medical Center</v>
+        <v>Tampa Port Authority</v>
       </c>
       <c r="F3" t="str">
         <v>1 person</v>
       </c>
       <c r="G3" t="str">
-        <v>+16125551234</v>
+        <v>+18135551234</v>
       </c>
       <c r="H3" t="str">
-        <v>Cardiologist</v>
+        <v>Port Operations Manager</v>
       </c>
       <c r="I3" t="str">
-        <v>2001 6th Street SE</v>
+        <v>1101 Channelside Drive</v>
       </c>
       <c r="J3" t="str">
-        <v>Minneapolis</v>
+        <v>Tampa</v>
       </c>
       <c r="K3" t="str">
-        <v>Minnesota</v>
+        <v>Florida</v>
       </c>
       <c r="L3" t="str">
-        <v>55455</v>
+        <v>33602</v>
       </c>
       <c r="M3" t="str">
         <v>United States</v>
@@ -570,7 +576,7 @@
         <v>30</v>
       </c>
       <c r="R3" t="str">
-        <v>FAILED</v>
+        <v/>
       </c>
       <c r="S3" t="str">
         <v/>
@@ -578,40 +584,40 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>quill.sterling@stlouisresearch.us</v>
+        <v>wilder.ash@pittsburghrobotics.us</v>
       </c>
       <c r="B4" t="str">
-        <v>BioQuill8901@StLouis</v>
+        <v>RoboticsWilder8901@Pittsburgh</v>
       </c>
       <c r="C4" t="str">
-        <v>Quill</v>
+        <v>Wilder</v>
       </c>
       <c r="D4" t="str">
-        <v>Sterling</v>
+        <v>Ash</v>
       </c>
       <c r="E4" t="str">
-        <v>St Louis Research Institute</v>
+        <v>Pittsburgh Robotics Lab</v>
       </c>
       <c r="F4" t="str">
         <v>1 person</v>
       </c>
       <c r="G4" t="str">
-        <v>+13145558901</v>
+        <v>+14125558901</v>
       </c>
       <c r="H4" t="str">
-        <v>Biomedical Researcher</v>
+        <v>Robotics Engineer</v>
       </c>
       <c r="I4" t="str">
-        <v>4444 Forest Park Avenue</v>
+        <v>4516 Henry Street</v>
       </c>
       <c r="J4" t="str">
-        <v>St Louis</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="K4" t="str">
-        <v>Missouri</v>
+        <v>Pennsylvania</v>
       </c>
       <c r="L4" t="str">
-        <v>63108</v>
+        <v>15213</v>
       </c>
       <c r="M4" t="str">
         <v>United States</v>
@@ -633,44 +639,47 @@
       </c>
       <c r="S4" t="str">
         <v/>
+      </c>
+      <c r="T4" t="str">
+        <v>Step: Saving payment - Error: PAYMENT_DECLINED: Check that the details in all fields are correct or try a different card.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>raven.black@baltimoremarine.us</v>
+        <v>xanthe.cross@clevelandclinic.us</v>
       </c>
       <c r="B5" t="str">
-        <v>MarineRaven6789@Baltimore</v>
+        <v>MedicalXanthe6789@Cleveland</v>
       </c>
       <c r="C5" t="str">
-        <v>Raven</v>
+        <v>Xanthe</v>
       </c>
       <c r="D5" t="str">
-        <v>Black</v>
+        <v>Cross</v>
       </c>
       <c r="E5" t="str">
-        <v>Baltimore Marine Institute</v>
+        <v>Cleveland Clinic</v>
       </c>
       <c r="F5" t="str">
         <v>1 person</v>
       </c>
       <c r="G5" t="str">
-        <v>+14105556789</v>
+        <v>+12165556789</v>
       </c>
       <c r="H5" t="str">
-        <v>Marine Biologist</v>
+        <v>Medical Researcher</v>
       </c>
       <c r="I5" t="str">
-        <v>601 East Pratt Street</v>
+        <v>9500 Euclid Avenue</v>
       </c>
       <c r="J5" t="str">
-        <v>Baltimore</v>
+        <v>Cleveland</v>
       </c>
       <c r="K5" t="str">
-        <v>Maryland</v>
+        <v>Ohio</v>
       </c>
       <c r="L5" t="str">
-        <v>21202</v>
+        <v>44195</v>
       </c>
       <c r="M5" t="str">
         <v>United States</v>
@@ -693,128 +702,13 @@
       <c r="S5" t="str">
         <v/>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>sylvan.reed@phoenixsolar.us</v>
-      </c>
-      <c r="B6" t="str">
-        <v>SolarSylvan1234@Phoenix</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Sylvan</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Reed</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Phoenix Solar Energy</v>
-      </c>
-      <c r="F6" t="str">
-        <v>1 person</v>
-      </c>
-      <c r="G6" t="str">
-        <v>+16025551234</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Solar Engineer</v>
-      </c>
-      <c r="I6" t="str">
-        <v>234 North Central Avenue</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Phoenix</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Arizona</v>
-      </c>
-      <c r="L6" t="str">
-        <v>85004</v>
-      </c>
-      <c r="M6" t="str">
-        <v>United States</v>
-      </c>
-      <c r="N6" t="str">
-        <v>5198939816602718</v>
-      </c>
-      <c r="O6" t="str">
-        <v>213</v>
-      </c>
-      <c r="P6" t="str">
-        <v>03</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>30</v>
-      </c>
-      <c r="R6" t="str">
-        <v>FAILED</v>
-      </c>
-      <c r="S6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>thorne.wilder@nashvillemusic.us</v>
-      </c>
-      <c r="B7" t="str">
-        <v>MusicThorne8901@Nashville</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Thorne</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Wilder</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Nashville Music Group</v>
-      </c>
-      <c r="F7" t="str">
-        <v>1 person</v>
-      </c>
-      <c r="G7" t="str">
-        <v>+16155558901</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Music Producer</v>
-      </c>
-      <c r="I7" t="str">
-        <v>222 5th Avenue South</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Nashville</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Tennessee</v>
-      </c>
-      <c r="L7" t="str">
-        <v>37203</v>
-      </c>
-      <c r="M7" t="str">
-        <v>United States</v>
-      </c>
-      <c r="N7" t="str">
-        <v>5198939816602718</v>
-      </c>
-      <c r="O7" t="str">
-        <v>213</v>
-      </c>
-      <c r="P7" t="str">
-        <v>03</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>30</v>
-      </c>
-      <c r="R7" t="str">
-        <v>FAILED</v>
-      </c>
-      <c r="S7" t="str">
-        <v/>
+      <c r="T5" t="str">
+        <v>Step: Confirming address (Stage 1) - Error: Microsoft error page detected after address confirmation</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T5"/>
   </ignoredErrors>
 </worksheet>
 </file>